--- a/docs/Tabelas - Copa do Mundo.xlsx
+++ b/docs/Tabelas - Copa do Mundo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\42941975870\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\42941975870\Documents\GitHub\bolao-copa-2026\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9FC2E0-9862-49BB-81AA-123CF00F3B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9276E4-82F8-4A45-815F-1A007FBC249C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{DC62366C-7472-44C3-AF96-9E31ABA80D67}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{DC62366C-7472-44C3-AF96-9E31ABA80D67}"/>
   </bookViews>
   <sheets>
     <sheet name="Classificação" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="63">
   <si>
     <t>GRUPO A</t>
   </si>
@@ -105,9 +105,6 @@
     <t>ÁFRICA DO SUL</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>MARROCOS</t>
   </si>
   <si>
@@ -217,6 +214,24 @@
   </si>
   <si>
     <t>PANAMÁ</t>
+  </si>
+  <si>
+    <t>TCHECA</t>
+  </si>
+  <si>
+    <t>BÓSNIA</t>
+  </si>
+  <si>
+    <t>TURQUIA</t>
+  </si>
+  <si>
+    <t>SUÉCIA</t>
+  </si>
+  <si>
+    <t>IRAQUE</t>
+  </si>
+  <si>
+    <t>RD CONGO</t>
   </si>
 </sst>
 </file>
@@ -908,19 +923,19 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
@@ -928,25 +943,25 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -954,25 +969,25 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -1032,25 +1047,25 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -1058,25 +1073,25 @@
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="L13" s="1">
         <v>0</v>
@@ -1084,25 +1099,25 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
@@ -1110,25 +1125,25 @@
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
@@ -1188,25 +1203,25 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -1214,25 +1229,25 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -1240,25 +1255,25 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="C22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -1266,25 +1281,25 @@
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
@@ -2439,18 +2454,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="N2:R2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="H10:L10"/>
+    <mergeCell ref="N10:R10"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="H18:L18"/>
     <mergeCell ref="N18:R18"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="H26:L26"/>
     <mergeCell ref="N26:R26"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="H10:L10"/>
-    <mergeCell ref="N10:R10"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
